--- a/search/extraction/calibration/extraction_E1_calibration_starter.xlsx
+++ b/search/extraction/calibration/extraction_E1_calibration_starter.xlsx
@@ -8153,7 +8153,7 @@
       </c>
       <c r="X3" s="7" t="inlineStr">
         <is>
-          <t>Acute / Chronic or intermittent / Acute on chronic / Asymptomatic / Mass only</t>
+          <t>Acute / Chronic or intermittent / Acute on chronic / Asymptomatic / Mass only；报告没写发作形式填 NR</t>
         </is>
       </c>
       <c r="Y3" s="7" t="inlineStr">
@@ -36941,7 +36941,7 @@
       <formula1>Lists!$I$2:$I$6</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X1503" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in list" error="值不在列表里。请从下拉列表选择；确需例外请在 Notes 里说明。" type="list" errorStyle="warning">
-      <formula1>Lists!$J$2:$J$6</formula1>
+      <formula1>Lists!$J$2:$J$7</formula1>
     </dataValidation>
     <dataValidation sqref="Z4:Z1503" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Number or NR" error="请填数字；报告里没有请填 NR。" type="custom" errorStyle="warning">
       <formula1>OR(ISNUMBER(Z4),Z4="NR")</formula1>
@@ -38871,6 +38871,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>No operation</t>
